--- a/lab02/APIO114_Lab02_2713963.xlsx
+++ b/lab02/APIO114_Lab02_2713963.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Dashboard" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">Dashboard!$A$1:$T$22</definedName>
+    <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">Dashboard!$A$1:$AC$22</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="78">
   <si>
     <t xml:space="preserve">Lab 2 Chart Choice and Visual Design</t>
   </si>
@@ -179,6 +179,9 @@
     <t xml:space="preserve">Orders: channels</t>
   </si>
   <si>
+    <t xml:space="preserve">Channel (largest first)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Design decision</t>
   </si>
   <si>
@@ -212,6 +215,12 @@
     <t xml:space="preserve">Chart 2 Revenue by channel</t>
   </si>
   <si>
+    <t xml:space="preserve">Chart 2 alternative – doughnut (backup)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Part-to-whole confirmed (channels = 100% of revenue, 480 orders). The doughnut is kept for reference: all three channels, slices sorted largest first from 12 o'clock, % labels on the slices, one highlight color, no gradient, 3D or exploded slices. Because the slices are nearly equal, the sorted bar chart is the main Chart 2.</t>
+  </si>
+  <si>
     <t xml:space="preserve">The data is part-to-whole: the three channels add up to the same total as the categories (SAR 35,467) and every order belongs to one channel (3 × 160 = 480 orders). However, the shares are very close (35.4%, 33.4%, 31.2%), so doughnut slices would look almost equal and be hard to compare. Following the lab rule, a sorted bar chart of percentage share was used instead of a doughnut.</t>
   </si>
   <si>
@@ -251,7 +260,7 @@
     <t xml:space="preserve">APIO 114 – Lab 2 Chart Choice and Visual Design  |  Student ID 2713963</t>
   </si>
   <si>
-    <t xml:space="preserve">Final corrected charts: category comparison and channel composition</t>
+    <t xml:space="preserve">Final corrected charts: category comparison, channel composition (sorted bar) and doughnut alternative for reference</t>
   </si>
 </sst>
 </file>
@@ -391,7 +400,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDEBF7"/>
-        <bgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFD5DCE6"/>
       </patternFill>
     </fill>
   </fills>
@@ -527,12 +536,12 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -577,7 +586,7 @@
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF1F5C8B"/>
-      <rgbColor rgb="FFD0D0D0"/>
+      <rgbColor rgb="FFD5DCE6"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -593,14 +602,14 @@
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFD0D0D0"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF4F81BD"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF1B365D"/>
       <rgbColor rgb="FF339966"/>
@@ -798,11 +807,11 @@
         </c:ser>
         <c:gapWidth val="55"/>
         <c:overlap val="0"/>
-        <c:axId val="9025491"/>
-        <c:axId val="11033005"/>
+        <c:axId val="32317593"/>
+        <c:axId val="23578775"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="9025491"/>
+        <c:axId val="32317593"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -834,7 +843,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11033005"/>
+        <c:crossAx val="23578775"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -842,7 +851,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="11033005"/>
+        <c:axId val="23578775"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -909,7 +918,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="9025491"/>
+        <c:crossAx val="32317593"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1114,11 +1123,11 @@
         </c:ser>
         <c:gapWidth val="55"/>
         <c:overlap val="0"/>
-        <c:axId val="6158267"/>
-        <c:axId val="23420973"/>
+        <c:axId val="30973237"/>
+        <c:axId val="717923"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="6158267"/>
+        <c:axId val="30973237"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1150,7 +1159,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="23420973"/>
+        <c:crossAx val="717923"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1158,7 +1167,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="23420973"/>
+        <c:axId val="717923"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -1225,7 +1234,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="6158267"/>
+        <c:crossAx val="30973237"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1254,6 +1263,273 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>Revenue share by channel</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:doughnutChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Chart Workspace'!K19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Revenue SAR</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4f81bd"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:explosion val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="1f5c8b"/>
+              </a:solidFill>
+              <a:ln w="19080">
+                <a:solidFill>
+                  <a:srgbClr val="ffffff"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="a9b7c9"/>
+              </a:solidFill>
+              <a:ln w="19080">
+                <a:solidFill>
+                  <a:srgbClr val="ffffff"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="d5dce6"/>
+              </a:solidFill>
+              <a:ln w="19080">
+                <a:solidFill>
+                  <a:srgbClr val="ffffff"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:txPr>
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="Calibri"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:separator>
+</c:separator>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:txPr>
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="Calibri"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:separator>
+</c:separator>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:txPr>
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="Calibri"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:separator>
+</c:separator>
+            </c:dLbl>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="1"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:separator>
+</c:separator>
+            <c:showLeaderLines val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Chart Workspace'!$J$20:$J$22</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Click and Collect</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Delivery</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>In Store</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Chart Workspace'!$K$20:$K$22</c:f>
+              <c:numCache>
+                <c:formatCode>"SAR "#,##0</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>12557</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>11838</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>11072</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:firstSliceAng val="0"/>
+        <c:holeSize val="50"/>
+      </c:doughnutChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="d9d9d9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -1384,11 +1660,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="13383268"/>
-        <c:axId val="19956579"/>
+        <c:axId val="82262247"/>
+        <c:axId val="81605395"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="13383268"/>
+        <c:axId val="82262247"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1420,7 +1696,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="19956579"/>
+        <c:crossAx val="81605395"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1428,7 +1704,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="19956579"/>
+        <c:axId val="81605395"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="13000"/>
@@ -1472,7 +1748,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="13383268"/>
+        <c:crossAx val="82262247"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1500,7 +1776,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -1677,11 +1953,11 @@
         </c:ser>
         <c:gapWidth val="55"/>
         <c:overlap val="0"/>
-        <c:axId val="88628349"/>
-        <c:axId val="67840449"/>
+        <c:axId val="93270546"/>
+        <c:axId val="44166114"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="88628349"/>
+        <c:axId val="93270546"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1713,7 +1989,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67840449"/>
+        <c:crossAx val="44166114"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1721,7 +1997,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="67840449"/>
+        <c:axId val="44166114"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -1788,7 +2064,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="88628349"/>
+        <c:crossAx val="93270546"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1816,7 +2092,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -1999,11 +2275,11 @@
         </c:ser>
         <c:gapWidth val="55"/>
         <c:overlap val="0"/>
-        <c:axId val="16235296"/>
-        <c:axId val="43559666"/>
+        <c:axId val="62049311"/>
+        <c:axId val="35964258"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="16235296"/>
+        <c:axId val="62049311"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2035,7 +2311,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43559666"/>
+        <c:crossAx val="35964258"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2043,7 +2319,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="43559666"/>
+        <c:axId val="35964258"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2110,7 +2386,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="16235296"/>
+        <c:crossAx val="62049311"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2138,7 +2414,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -2315,11 +2591,11 @@
         </c:ser>
         <c:gapWidth val="55"/>
         <c:overlap val="0"/>
-        <c:axId val="26664629"/>
-        <c:axId val="7341642"/>
+        <c:axId val="98401865"/>
+        <c:axId val="59230428"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="26664629"/>
+        <c:axId val="98401865"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2351,7 +2627,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7341642"/>
+        <c:crossAx val="59230428"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2359,7 +2635,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="7341642"/>
+        <c:axId val="59230428"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2426,10 +2702,277 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26664629"/>
+        <c:crossAx val="98401865"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="d9d9d9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>Doughnut alternative: shares are nearly equal</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:doughnutChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Chart Workspace'!K19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Revenue SAR</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4f81bd"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:explosion val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="1f5c8b"/>
+              </a:solidFill>
+              <a:ln w="19080">
+                <a:solidFill>
+                  <a:srgbClr val="ffffff"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="a9b7c9"/>
+              </a:solidFill>
+              <a:ln w="19080">
+                <a:solidFill>
+                  <a:srgbClr val="ffffff"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="d5dce6"/>
+              </a:solidFill>
+              <a:ln w="19080">
+                <a:solidFill>
+                  <a:srgbClr val="ffffff"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:txPr>
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="Calibri"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:separator>
+</c:separator>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:txPr>
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="Calibri"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:separator>
+</c:separator>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:txPr>
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="Calibri"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:separator>
+</c:separator>
+            </c:dLbl>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="1"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:separator>
+</c:separator>
+            <c:showLeaderLines val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Chart Workspace'!$J$20:$J$22</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Click and Collect</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Delivery</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>In Store</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Chart Workspace'!$K$20:$K$22</c:f>
+              <c:numCache>
+                <c:formatCode>"SAR "#,##0</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>12557</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>11838</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>11072</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:firstSliceAng val="0"/>
+        <c:holeSize val="50"/>
+      </c:doughnutChart>
       <c:spPr>
         <a:noFill/>
         <a:ln w="0">
@@ -2490,14 +3033,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>78120</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>128520</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>32760</xdr:rowOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>110880</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2518,16 +3061,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>78120</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>128520</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>32760</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>231840</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>110880</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2535,8 +3078,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="14725800"/>
-        <a:ext cx="6119640" cy="2699640"/>
+        <a:off x="7260120" y="7562880"/>
+        <a:ext cx="4319640" cy="2699640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2550,18 +3093,48 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>78120</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>128520</xdr:colOff>
-      <xdr:row>89</xdr:row>
-      <xdr:rowOff>32760</xdr:rowOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>110880</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="3" name="Chart 4"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="14725800"/>
+        <a:ext cx="6119640" cy="2699640"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>78120</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>128520</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>110880</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 5"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -2570,7 +3143,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2596,7 +3169,7 @@
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 1"/>
+        <xdr:cNvPr id="5" name="Chart 1"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -2626,7 +3199,7 @@
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Chart 2"/>
+        <xdr:cNvPr id="6" name="Chart 2"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -2636,6 +3209,36 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>176040</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>290880</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>187560</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 3"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="12230280" y="571680"/>
+        <a:ext cx="3959640" cy="3059640"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3179,6 +3782,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3343,49 +3947,98 @@
         <v>480</v>
       </c>
     </row>
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J19" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J20" s="4" t="str">
+        <f aca="false">INDEX('Channel Composition'!$A$5:$A$7,MATCH(K20,'Channel Composition'!$B$5:$B$7,0))</f>
+        <v>Click and Collect</v>
+      </c>
+      <c r="K20" s="14" t="n">
+        <f aca="false">LARGE('Channel Composition'!$B$5:$B$7,1)</f>
+        <v>12557</v>
+      </c>
+      <c r="L20" s="15" t="n">
+        <f aca="false">K20/SUM('Channel Composition'!$B$5:$B$7)</f>
+        <v>0.354047424366312</v>
+      </c>
+    </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="J21" s="4" t="str">
+        <f aca="false">INDEX('Channel Composition'!$A$5:$A$7,MATCH(K21,'Channel Composition'!$B$5:$B$7,0))</f>
+        <v>Delivery</v>
+      </c>
+      <c r="K21" s="14" t="n">
+        <f aca="false">LARGE('Channel Composition'!$B$5:$B$7,2)</f>
+        <v>11838</v>
+      </c>
+      <c r="L21" s="15" t="n">
+        <f aca="false">K21/SUM('Channel Composition'!$B$5:$B$7)</f>
+        <v>0.333775058505089</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="J22" s="4" t="str">
+        <f aca="false">INDEX('Channel Composition'!$A$5:$A$7,MATCH(K22,'Channel Composition'!$B$5:$B$7,0))</f>
+        <v>In Store</v>
+      </c>
+      <c r="K22" s="14" t="n">
+        <f aca="false">LARGE('Channel Composition'!$B$5:$B$7,3)</f>
+        <v>11072</v>
+      </c>
+      <c r="L22" s="15" t="n">
+        <f aca="false">K22/SUM('Channel Composition'!$B$5:$B$7)</f>
+        <v>0.312177517128598</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="20" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
@@ -3394,50 +4047,70 @@
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J27" s="10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>51</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="J44" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="K44" s="22"/>
+      <c r="L44" s="22"/>
     </row>
     <row r="45" customFormat="false" ht="97.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B45" s="21" t="s">
-        <v>61</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="J45" s="22"/>
+      <c r="K45" s="22"/>
+      <c r="L45" s="22"/>
     </row>
     <row r="46" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="20" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>62</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="J46" s="22"/>
+      <c r="K46" s="22"/>
+      <c r="L46" s="22"/>
     </row>
     <row r="47" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B47" s="21" t="s">
-        <v>63</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="J47" s="22"/>
+      <c r="K47" s="22"/>
+      <c r="L47" s="22"/>
     </row>
     <row r="48" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B48" s="21" t="s">
-        <v>64</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="J48" s="22"/>
+      <c r="K48" s="22"/>
+      <c r="L48" s="22"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
@@ -3448,63 +4121,64 @@
       <c r="H50" s="6"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="22" t="s">
-        <v>66</v>
+      <c r="A51" s="23" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="10" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="23" t="s">
-        <v>68</v>
-      </c>
-      <c r="B69" s="23"/>
-      <c r="C69" s="23"/>
-      <c r="D69" s="23"/>
-      <c r="E69" s="23"/>
-      <c r="F69" s="23"/>
-      <c r="G69" s="23"/>
-      <c r="H69" s="23"/>
+      <c r="A69" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="B69" s="22"/>
+      <c r="C69" s="22"/>
+      <c r="D69" s="22"/>
+      <c r="E69" s="22"/>
+      <c r="F69" s="22"/>
+      <c r="G69" s="22"/>
+      <c r="H69" s="22"/>
     </row>
     <row r="70" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="B70" s="23"/>
-      <c r="C70" s="23"/>
-      <c r="D70" s="23"/>
-      <c r="E70" s="23"/>
-      <c r="F70" s="23"/>
-      <c r="G70" s="23"/>
-      <c r="H70" s="23"/>
+      <c r="A70" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="B70" s="22"/>
+      <c r="C70" s="22"/>
+      <c r="D70" s="22"/>
+      <c r="E70" s="22"/>
+      <c r="F70" s="22"/>
+      <c r="G70" s="22"/>
+      <c r="H70" s="22"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="10" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="B73" s="23"/>
-      <c r="C73" s="23"/>
-      <c r="D73" s="23"/>
-      <c r="E73" s="23"/>
-      <c r="F73" s="23"/>
-      <c r="G73" s="23"/>
-      <c r="H73" s="23"/>
+      <c r="A73" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="B73" s="22"/>
+      <c r="C73" s="22"/>
+      <c r="D73" s="22"/>
+      <c r="E73" s="22"/>
+      <c r="F73" s="22"/>
+      <c r="G73" s="22"/>
+      <c r="H73" s="22"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="24" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
+    <mergeCell ref="J44:L48"/>
     <mergeCell ref="A69:H69"/>
     <mergeCell ref="A70:H70"/>
     <mergeCell ref="A73:H73"/>
@@ -3530,12 +4204,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="25" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/lab02/APIO114_Lab02_2713963.xlsx
+++ b/lab02/APIO114_Lab02_2713963.xlsx
@@ -8,16 +8,12 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
-    <sheet name="Instructions" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Category Performance" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Channel Composition" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Start Here" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Category Summary" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Channel Summary" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Chart Workspace" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Dashboard" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
-  <definedNames>
-    <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">Dashboard!$A$1:$AC$22</definedName>
-  </definedNames>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr iterateCount="0" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -27,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="69">
   <si>
     <t xml:space="preserve">Lab 2 Chart Choice and Visual Design</t>
   </si>
@@ -35,16 +31,7 @@
     <t xml:space="preserve">APIO 114 Data Visualization | Semester 2027-01</t>
   </si>
   <si>
-    <t xml:space="preserve">Student name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اروى حمدان الحربي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2713963</t>
+    <t xml:space="preserve">Student: اروى حمدان الحربي  |  ID: 2713963</t>
   </si>
   <si>
     <t xml:space="preserve">Duration</t>
@@ -62,7 +49,7 @@
     <t xml:space="preserve">Save as</t>
   </si>
   <si>
-    <t xml:space="preserve">APIO114_Lab02_2713963.xlsx</t>
+    <t xml:space="preserve">APIO114_Lab02_StudentID.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Submission</t>
@@ -92,7 +79,10 @@
     <t xml:space="preserve">Compare category performance with a sorted horizontal bar chart.</t>
   </si>
   <si>
-    <t xml:space="preserve">Show channel composition with a doughnut chart only after confirming part-to-whole.</t>
+    <t xml:space="preserve">Done</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Show channel composition with a doughnut chart only after confirming part-to-whole meaning.</t>
   </si>
   <si>
     <t xml:space="preserve">Apply Gestalt similarity and proximity to group related elements.</t>
@@ -137,7 +127,7 @@
     <t xml:space="preserve">Channel Composition</t>
   </si>
   <si>
-    <t xml:space="preserve">Use this part-to-whole data only if the resulting chart remains easy</t>
+    <t xml:space="preserve">Use this part-to-whole data only if the resulting chart remains easy to compare.</t>
   </si>
   <si>
     <t xml:space="preserve">Channel</t>
@@ -158,28 +148,28 @@
     <t xml:space="preserve">Create the required charts and record your design decisions.</t>
   </si>
   <si>
-    <t xml:space="preserve">Chart helper tables (formulas – sorted from the source sheets)</t>
+    <t xml:space="preserve">Chart helper tables – formulas sorted from the summary sheets (source sheets unchanged)</t>
   </si>
   <si>
     <t xml:space="preserve">Chart 1 Revenue by category</t>
   </si>
   <si>
+    <t xml:space="preserve">Chart 2 Revenue by channel</t>
+  </si>
+  <si>
     <t xml:space="preserve">Share</t>
   </si>
   <si>
-    <t xml:space="preserve">Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check: category total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orders: categories</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orders: channels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Channel (largest first)</t>
+    <t xml:space="preserve">Channel total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Category total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orders (channels)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orders (categories)</t>
   </si>
   <si>
     <t xml:space="preserve">Design decision</t>
@@ -191,58 +181,46 @@
     <t xml:space="preserve">Chart choice</t>
   </si>
   <si>
-    <t xml:space="preserve">A horizontal bar chart, because the question is a comparison between categories. Viewers compare bar lengths on a common zero baseline very accurately, and the horizontal layout keeps the category names easy to read.</t>
+    <t xml:space="preserve">Chart 1: horizontal bar chart, because the question is a comparison between categories; bar lengths on a common zero baseline are easy to compare and the category names stay readable. Chart 2: the channels are part-to-whole (they add up to the same total revenue, SAR 35,466, and 480 orders), but the shares are very close (35.4%, 33.4%, 31.2%), so doughnut slices would look almost equal. A sorted bar chart of share is therefore the main Chart 2; the doughnut is kept below as an alternative.</t>
   </si>
   <si>
     <t xml:space="preserve">Order</t>
   </si>
   <si>
-    <t xml:space="preserve">Bars are sorted by revenue from highest (Meals, SAR 11,864) to lowest (Snacks, SAR 6,567), so the chart reads as a ranking and bar length and labels show the same order.</t>
+    <t xml:space="preserve">Chart 1 is sorted from highest revenue (Meals, SAR 11,864) to lowest (Snacks, SAR 6,567), so bar length and labels show the same ranking. Chart 2 is sorted from the largest share (Click and Collect) to the smallest (In Store), so the largest channel is found in under five seconds.</t>
   </si>
   <si>
     <t xml:space="preserve">Color</t>
   </si>
   <si>
-    <t xml:space="preserve">One neutral grey-blue hue for all bars (Gestalt similarity: same color = same kind of item). Only Meals, the category named in the title, is highlighted in dark blue as the single preattentive accent.</t>
+    <t xml:space="preserve">One neutral grey-blue hue for all bars (Gestalt similarity: same color = same kind of item). Only the item named in each title is highlighted in dark blue (Meals in Chart 1, Click and Collect in Chart 2) as the single preattentive accent. Flat colors, no gradients or 3D.</t>
   </si>
   <si>
     <t xml:space="preserve">Labels and scale</t>
   </si>
   <si>
-    <t xml:space="preserve">Revenue values are labelled directly at the end of each bar (Gestalt proximity), so the legend was removed because it only repeated the category names. The value axis starts at 0 so bar length is proportional to revenue; no gridlines, 3D or gradients.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chart 2 Revenue by channel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chart 2 alternative – doughnut (backup)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Part-to-whole confirmed (channels = 100% of revenue, 480 orders). The doughnut is kept for reference: all three channels, slices sorted largest first from 12 o'clock, % labels on the slices, one highlight color, no gradient, 3D or exploded slices. Because the slices are nearly equal, the sorted bar chart is the main Chart 2.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The data is part-to-whole: the three channels add up to the same total as the categories (SAR 35,467) and every order belongs to one channel (3 × 160 = 480 orders). However, the shares are very close (35.4%, 33.4%, 31.2%), so doughnut slices would look almost equal and be hard to compare. Following the lab rule, a sorted bar chart of percentage share was used instead of a doughnut.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Channels are sorted from the largest share (Click and Collect) to the smallest (In Store), so the largest channel is the top bar and can be found in under five seconds.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All bars share one grey-blue hue (similarity); only Click and Collect, named in the title, is highlighted in dark blue. Flat colors with good contrast – no gradients, 3D or exploded slices.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Each bar is labelled directly with its percentage share (proximity), so no legend is needed. The axis starts at 0% so the small differences between channels are shown honestly.</t>
+    <t xml:space="preserve">Values are labelled directly at the end of each bar (Gestalt proximity), so the legend was removed because it only repeated the labels. Both value axes start at zero (SAR 0 and 0%) so bar length is proportional to the value; gridlines and chart junk were removed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chart 2 alternative – doughnut (part-to-whole confirmed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Part-to-whole confirmed: the three channels make up 100% of revenue and every order belongs to one channel. Doughnut rules applied: all three channels kept, slices sorted largest first from 12 o'clock, percentage labels on the slices, one highlight color, no gradient, 3D or exploded slices. Because the slices are nearly equal, the sorted bar chart above is used as the main Chart 2.</t>
   </si>
   <si>
     <t xml:space="preserve">Misleading chart – diagnose and repair</t>
   </si>
   <si>
-    <t xml:space="preserve">A) Misleading version (duplicate of the channel chart with the value axis truncated at SAR 10,000) – not part of the final charts</t>
+    <t xml:space="preserve">A) Misleading version: duplicate of the channel chart with the value axis truncated at SAR 10,000 (not a final chart)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B) Corrected version: axis starts at zero (retained for submission)</t>
   </si>
   <si>
     <t xml:space="preserve">How the change distorts perception</t>
   </si>
   <si>
-    <t xml:space="preserve">Because the value axis starts at SAR 10,000 instead of 0, the visible part of the Click and Collect bar (2,557) is about 2.4 times the In Store bar (1,072), so it looks more than twice as large even though its revenue is only about 13% higher (SAR 12,557 vs SAR 11,072).</t>
+    <t xml:space="preserve">Because the value axis starts at SAR 10,000 instead of 0, the visible part of the Click and Collect bar (about 2,557) is about 2.4 times the In Store bar (about 1,072), so Click and Collect looks more than twice as large even though its revenue is only about 13% higher (SAR 12,557 vs SAR 11,072).</t>
   </si>
   <si>
     <t xml:space="preserve">Viewers judge bars by their length rather than by reading the axis numbers, so the truncated axis exaggerates small differences and makes In Store look like a weak channel when all three channels are actually close.</t>
@@ -251,35 +229,24 @@
     <t xml:space="preserve">How it was corrected</t>
   </si>
   <si>
-    <t xml:space="preserve">The axis minimum was reset to 0, the bars were sorted from largest to smallest, values were labelled directly, the title was rewritten to state the real finding, and only the leading channel is highlighted. The corrected version is kept below for submission.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B) Corrected version (axis starts at 0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APIO 114 – Lab 2 Chart Choice and Visual Design  |  Student ID 2713963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final corrected charts: category comparison, channel composition (sorted bar) and doughnut alternative for reference</t>
+    <t xml:space="preserve">The axis minimum was reset to 0, the bars were sorted from largest to smallest, values were labelled directly, the title was rewritten to state the real finding, and only the leading channel is highlighted. The corrected chart is kept for submission.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="&quot;SAR &quot;#,##0"/>
-    <numFmt numFmtId="166" formatCode="0"/>
-    <numFmt numFmtId="167" formatCode="0.00"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="0.00"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="18">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -299,9 +266,48 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="11"/>
+      <sz val="10"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="10"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
@@ -313,10 +319,9 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
@@ -328,6 +333,7 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
+      <color rgb="FFC00000"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -336,21 +342,6 @@
       <b val="true"/>
       <sz val="10"/>
       <color rgb="FF008000"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FFC00000"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -375,16 +366,8 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
-    <font>
-      <b val="true"/>
-      <sz val="13"/>
-      <color rgb="FF1B365D"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -393,18 +376,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1B365D"/>
-        <bgColor rgb="FF333333"/>
+        <fgColor rgb="FF17365D"/>
+        <bgColor rgb="FF333399"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
-        <bgColor rgb="FFD5DCE6"/>
+        <fgColor rgb="FFD9EAF7"/>
+        <bgColor rgb="FFE2F0D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAFAFA"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="15">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -417,8 +406,163 @@
       <right/>
       <top/>
       <bottom style="thin">
-        <color rgb="FFD0D0D0"/>
+        <color rgb="FF17365D"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -447,108 +591,172 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="42">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -561,6 +769,50 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF375623"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF17365D"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF222222"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -576,13 +828,13 @@
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF156082"/>
       <rgbColor rgb="FFA9B7C9"/>
-      <rgbColor rgb="FF878787"/>
+      <rgbColor rgb="FF8B8B8B"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFDDEBF7"/>
+      <rgbColor rgb="FFFAFAFA"/>
+      <rgbColor rgb="FFD9EAF7"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF1F5C8B"/>
@@ -597,28 +849,28 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFD9D9D9"/>
+      <rgbColor rgb="FFE2F0D9"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFD0D0D0"/>
-      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FFD9D9D9"/>
+      <rgbColor rgb="FF4472C4"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFE6B800"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF4F81BD"/>
+      <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF1B365D"/>
+      <rgbColor rgb="FF17365D"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF375623"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="FF222222"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -641,6 +893,7 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
@@ -649,6 +902,7 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
               </a:rPr>
               <a:t>Meals earn the highest revenue of all categories</a:t>
             </a:r>
@@ -674,7 +928,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Chart Workspace'!K4</c:f>
+              <c:f>'Chart Workspace'!Q5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -745,6 +999,7 @@
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
                     <a:latin typeface="Calibri"/>
+                    <a:ea typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
@@ -765,7 +1020,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Chart Workspace'!$J$5:$J$8</c:f>
+              <c:f>'Chart Workspace'!$P$6:$P$9</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -785,7 +1040,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Chart Workspace'!$K$5:$K$8</c:f>
+              <c:f>'Chart Workspace'!$Q$6:$Q$9</c:f>
               <c:numCache>
                 <c:formatCode>"SAR "#,##0</c:formatCode>
                 <c:ptCount val="4"/>
@@ -793,13 +1048,13 @@
                   <c:v>6567</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6994</c:v>
+                  <c:v>6993.6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>10042</c:v>
+                  <c:v>10041.7</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11864</c:v>
+                  <c:v>11863.8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -807,11 +1062,11 @@
         </c:ser>
         <c:gapWidth val="55"/>
         <c:overlap val="0"/>
-        <c:axId val="32317593"/>
-        <c:axId val="23578775"/>
+        <c:axId val="40541759"/>
+        <c:axId val="46134616"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="32317593"/>
+        <c:axId val="40541759"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -822,9 +1077,9 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln w="9360">
+          <a:ln w="12600">
             <a:solidFill>
-              <a:srgbClr val="878787"/>
+              <a:srgbClr val="8b8b8b"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -839,11 +1094,12 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="23578775"/>
+        <c:crossAx val="46134616"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -851,7 +1107,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="23578775"/>
+        <c:axId val="46134616"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -870,6 +1126,7 @@
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
                     <a:latin typeface="Calibri"/>
+                    <a:ea typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
@@ -878,6 +1135,7 @@
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
                     <a:latin typeface="Calibri"/>
+                    <a:ea typeface="Calibri"/>
                   </a:rPr>
                   <a:t>Revenue (SAR)</a:t>
                 </a:r>
@@ -897,9 +1155,9 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln w="9360">
+          <a:ln w="12600">
             <a:solidFill>
-              <a:srgbClr val="878787"/>
+              <a:srgbClr val="8b8b8b"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -914,11 +1172,12 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="32317593"/>
+        <c:crossAx val="40541759"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -963,6 +1222,7 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
@@ -971,8 +1231,9 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
               </a:rPr>
-              <a:t>Click and Collect brings in the largest share of revenue, but all three channels are close</a:t>
+              <a:t>Click and Collect leads, but all three channels are close</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -996,7 +1257,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Chart Workspace'!L10</c:f>
+              <c:f>'Chart Workspace'!R11</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1067,6 +1328,7 @@
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
                     <a:latin typeface="Calibri"/>
+                    <a:ea typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
@@ -1087,7 +1349,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Chart Workspace'!$J$11:$J$13</c:f>
+              <c:f>'Chart Workspace'!$P$12:$P$14</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -1104,18 +1366,18 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Chart Workspace'!$L$11:$L$13</c:f>
+              <c:f>'Chart Workspace'!$R$12:$R$14</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>0.312177517128598</c:v>
+                  <c:v>0.312179799865223</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.333775058505089</c:v>
+                  <c:v>0.33377506971446</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.354047424366312</c:v>
+                  <c:v>0.354045130420317</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1123,11 +1385,11 @@
         </c:ser>
         <c:gapWidth val="55"/>
         <c:overlap val="0"/>
-        <c:axId val="30973237"/>
-        <c:axId val="717923"/>
+        <c:axId val="19682116"/>
+        <c:axId val="80492597"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="30973237"/>
+        <c:axId val="19682116"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1138,9 +1400,9 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln w="9360">
+          <a:ln w="12600">
             <a:solidFill>
-              <a:srgbClr val="878787"/>
+              <a:srgbClr val="8b8b8b"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -1155,11 +1417,12 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="717923"/>
+        <c:crossAx val="80492597"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1167,7 +1430,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="717923"/>
+        <c:axId val="80492597"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -1186,6 +1449,7 @@
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
                     <a:latin typeface="Calibri"/>
+                    <a:ea typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
@@ -1194,6 +1458,7 @@
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
                     <a:latin typeface="Calibri"/>
+                    <a:ea typeface="Calibri"/>
                   </a:rPr>
                   <a:t>Share of total revenue</a:t>
                 </a:r>
@@ -1213,9 +1478,9 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln w="9360">
+          <a:ln w="12600">
             <a:solidFill>
-              <a:srgbClr val="878787"/>
+              <a:srgbClr val="8b8b8b"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -1230,11 +1495,12 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="30973237"/>
+        <c:crossAx val="19682116"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1279,6 +1545,7 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
@@ -1287,8 +1554,9 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
               </a:rPr>
-              <a:t>Revenue share by channel</a:t>
+              <a:t>Revenue share by channel (doughnut)</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1310,7 +1578,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Chart Workspace'!K19</c:f>
+              <c:f>'Channel Summary'!B5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1321,7 +1589,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="4f81bd"/>
+              <a:srgbClr val="156082"/>
             </a:solidFill>
             <a:ln w="0">
               <a:noFill/>
@@ -1453,6 +1721,7 @@
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
                     <a:latin typeface="Calibri"/>
+                    <a:ea typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
@@ -1468,7 +1737,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Chart Workspace'!$J$20:$J$22</c:f>
+              <c:f>'Channel Summary'!$A$6:$A$8</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -1485,18 +1754,18 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Chart Workspace'!$K$20:$K$22</c:f>
+              <c:f>'Channel Summary'!$B$6:$B$8</c:f>
               <c:numCache>
                 <c:formatCode>"SAR "#,##0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>12557</c:v>
+                  <c:v>12556.6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11838</c:v>
+                  <c:v>11837.7</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11072</c:v>
+                  <c:v>11071.8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1546,6 +1815,7 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
@@ -1554,6 +1824,7 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
               </a:rPr>
               <a:t>Click and Collect far outsells In Store (misleading)</a:t>
             </a:r>
@@ -1579,7 +1850,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Channel Composition'!B4</c:f>
+              <c:f>'Channel Summary'!B5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1624,7 +1895,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Channel Composition'!$A$5:$A$7</c:f>
+              <c:f>'Channel Summary'!$A$6:$A$8</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -1641,18 +1912,18 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Channel Composition'!$B$5:$B$7</c:f>
+              <c:f>'Channel Summary'!$B$6:$B$8</c:f>
               <c:numCache>
                 <c:formatCode>"SAR "#,##0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>12557</c:v>
+                  <c:v>12556.6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11838</c:v>
+                  <c:v>11837.7</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11072</c:v>
+                  <c:v>11071.8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1660,11 +1931,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="82262247"/>
-        <c:axId val="81605395"/>
+        <c:axId val="50166213"/>
+        <c:axId val="70985252"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="82262247"/>
+        <c:axId val="50166213"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1675,9 +1946,9 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln w="9360">
+          <a:ln w="12600">
             <a:solidFill>
-              <a:srgbClr val="878787"/>
+              <a:srgbClr val="8b8b8b"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -1692,11 +1963,12 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81605395"/>
+        <c:crossAx val="70985252"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1704,7 +1976,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="81605395"/>
+        <c:axId val="70985252"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="13000"/>
@@ -1714,9 +1986,9 @@
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="9360">
+            <a:ln w="12600">
               <a:solidFill>
-                <a:srgbClr val="878787"/>
+                <a:srgbClr val="8b8b8b"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1727,9 +1999,9 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln w="9360">
+          <a:ln w="12600">
             <a:solidFill>
-              <a:srgbClr val="878787"/>
+              <a:srgbClr val="8b8b8b"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -1744,11 +2016,12 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="82262247"/>
+        <c:crossAx val="50166213"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1793,6 +2066,7 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
@@ -1801,8 +2075,9 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
               </a:rPr>
-              <a:t>Click and Collect earns the most revenue, only slightly ahead of the other channels</a:t>
+              <a:t>Click and Collect earns the most revenue, only slightly ahead of the others</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1826,7 +2101,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Chart Workspace'!K10</c:f>
+              <c:f>'Chart Workspace'!Q11</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1897,6 +2172,7 @@
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
                     <a:latin typeface="Calibri"/>
+                    <a:ea typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
@@ -1917,7 +2193,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Chart Workspace'!$J$11:$J$13</c:f>
+              <c:f>'Chart Workspace'!$P$12:$P$14</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -1934,18 +2210,18 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Chart Workspace'!$K$11:$K$13</c:f>
+              <c:f>'Chart Workspace'!$Q$12:$Q$14</c:f>
               <c:numCache>
                 <c:formatCode>"SAR "#,##0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>11072</c:v>
+                  <c:v>11071.8</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11838</c:v>
+                  <c:v>11837.7</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>12557</c:v>
+                  <c:v>12556.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1953,11 +2229,11 @@
         </c:ser>
         <c:gapWidth val="55"/>
         <c:overlap val="0"/>
-        <c:axId val="93270546"/>
-        <c:axId val="44166114"/>
+        <c:axId val="29310303"/>
+        <c:axId val="64952816"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="93270546"/>
+        <c:axId val="29310303"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1968,9 +2244,9 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln w="9360">
+          <a:ln w="12600">
             <a:solidFill>
-              <a:srgbClr val="878787"/>
+              <a:srgbClr val="8b8b8b"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -1985,11 +2261,12 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44166114"/>
+        <c:crossAx val="64952816"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1997,7 +2274,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="44166114"/>
+        <c:axId val="64952816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2016,6 +2293,7 @@
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
                     <a:latin typeface="Calibri"/>
+                    <a:ea typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
@@ -2024,6 +2302,7 @@
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
                     <a:latin typeface="Calibri"/>
+                    <a:ea typeface="Calibri"/>
                   </a:rPr>
                   <a:t>Revenue (SAR)</a:t>
                 </a:r>
@@ -2043,9 +2322,9 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln w="9360">
+          <a:ln w="12600">
             <a:solidFill>
-              <a:srgbClr val="878787"/>
+              <a:srgbClr val="8b8b8b"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -2060,919 +2339,15 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="93270546"/>
+        <c:crossAx val="29310303"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:srgbClr val="ffffff"/>
-    </a:solidFill>
-    <a:ln w="9360">
-      <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-  </c:spPr>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Meals earn the highest revenue of all categories</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:barChart>
-        <c:barDir val="bar"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Chart Workspace'!K4</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Revenue SAR</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="a9b7c9"/>
-            </a:solidFill>
-            <a:ln w="0">
-              <a:solidFill>
-                <a:srgbClr val="a9b7c9"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dPt>
-            <c:idx val="3"/>
-            <c:invertIfNegative val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="1f5c8b"/>
-              </a:solidFill>
-              <a:ln w="0">
-                <a:solidFill>
-                  <a:srgbClr val="1f5c8b"/>
-                </a:solidFill>
-              </a:ln>
-            </c:spPr>
-          </c:dPt>
-          <c:dLbls>
-            <c:numFmt formatCode="&quot;SAR &quot;#,##0" sourceLinked="1"/>
-            <c:dLbl>
-              <c:idx val="3"/>
-              <c:numFmt formatCode="&quot;SAR &quot;#,##0" sourceLinked="1"/>
-              <c:txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:latin typeface="Calibri"/>
-                    </a:defRPr>
-                  </a:pPr>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="outEnd"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:separator>; </c:separator>
-            </c:dLbl>
-            <c:txPr>
-              <a:bodyPr wrap="square"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Chart Workspace'!$J$5:$J$8</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Snacks</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Beverages</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Desserts</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Meals</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Chart Workspace'!$K$5:$K$8</c:f>
-              <c:numCache>
-                <c:formatCode>"SAR "#,##0</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>6567</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>6994</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>10042</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>11864</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:gapWidth val="55"/>
-        <c:overlap val="0"/>
-        <c:axId val="62049311"/>
-        <c:axId val="35964258"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="62049311"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:ln w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="35964258"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="35964258"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:min val="0"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>Revenue (SAR)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="0">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-        </c:title>
-        <c:numFmt formatCode="&quot;SAR &quot;#,##0" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:ln w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="62049311"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:srgbClr val="ffffff"/>
-    </a:solidFill>
-    <a:ln w="9360">
-      <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-  </c:spPr>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Click and Collect brings in the largest share, but channels are close</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:barChart>
-        <c:barDir val="bar"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Chart Workspace'!L10</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Share</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="a9b7c9"/>
-            </a:solidFill>
-            <a:ln w="0">
-              <a:solidFill>
-                <a:srgbClr val="a9b7c9"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dPt>
-            <c:idx val="2"/>
-            <c:invertIfNegative val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="1f5c8b"/>
-              </a:solidFill>
-              <a:ln w="0">
-                <a:solidFill>
-                  <a:srgbClr val="1f5c8b"/>
-                </a:solidFill>
-              </a:ln>
-            </c:spPr>
-          </c:dPt>
-          <c:dLbls>
-            <c:numFmt formatCode="0.0%" sourceLinked="1"/>
-            <c:dLbl>
-              <c:idx val="2"/>
-              <c:numFmt formatCode="0.0%" sourceLinked="1"/>
-              <c:txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:latin typeface="Calibri"/>
-                    </a:defRPr>
-                  </a:pPr>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="outEnd"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:separator>; </c:separator>
-            </c:dLbl>
-            <c:txPr>
-              <a:bodyPr wrap="square"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Chart Workspace'!$J$11:$J$13</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>In Store</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Delivery</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Click and Collect</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Chart Workspace'!$L$11:$L$13</c:f>
-              <c:numCache>
-                <c:formatCode>0.0%</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>0.312177517128598</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.333775058505089</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.354047424366312</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:gapWidth val="55"/>
-        <c:overlap val="0"/>
-        <c:axId val="98401865"/>
-        <c:axId val="59230428"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="98401865"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:ln w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="59230428"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="59230428"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:min val="0"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>Share of total revenue</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="0">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-        </c:title>
-        <c:numFmt formatCode="0.0%" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:ln w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="98401865"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:srgbClr val="ffffff"/>
-    </a:solidFill>
-    <a:ln w="9360">
-      <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-  </c:spPr>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Doughnut alternative: shares are nearly equal</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:doughnutChart>
-        <c:varyColors val="1"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Chart Workspace'!K19</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Revenue SAR</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="4f81bd"/>
-            </a:solidFill>
-            <a:ln w="0">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:explosion val="0"/>
-          <c:dPt>
-            <c:idx val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="1f5c8b"/>
-              </a:solidFill>
-              <a:ln w="19080">
-                <a:solidFill>
-                  <a:srgbClr val="ffffff"/>
-                </a:solidFill>
-                <a:round/>
-              </a:ln>
-            </c:spPr>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="1"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="a9b7c9"/>
-              </a:solidFill>
-              <a:ln w="19080">
-                <a:solidFill>
-                  <a:srgbClr val="ffffff"/>
-                </a:solidFill>
-                <a:round/>
-              </a:ln>
-            </c:spPr>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="2"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="d5dce6"/>
-              </a:solidFill>
-              <a:ln w="19080">
-                <a:solidFill>
-                  <a:srgbClr val="ffffff"/>
-                </a:solidFill>
-                <a:round/>
-              </a:ln>
-            </c:spPr>
-          </c:dPt>
-          <c:dLbls>
-            <c:dLbl>
-              <c:idx val="0"/>
-              <c:txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:latin typeface="Calibri"/>
-                    </a:defRPr>
-                  </a:pPr>
-                </a:p>
-              </c:txPr>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="1"/>
-              <c:separator>
-</c:separator>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="1"/>
-              <c:txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:latin typeface="Calibri"/>
-                    </a:defRPr>
-                  </a:pPr>
-                </a:p>
-              </c:txPr>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="1"/>
-              <c:separator>
-</c:separator>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="2"/>
-              <c:txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:latin typeface="Calibri"/>
-                    </a:defRPr>
-                  </a:pPr>
-                </a:p>
-              </c:txPr>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="1"/>
-              <c:separator>
-</c:separator>
-            </c:dLbl>
-            <c:txPr>
-              <a:bodyPr wrap="square"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="1"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="1"/>
-            <c:separator>
-</c:separator>
-            <c:showLeaderLines val="1"/>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Chart Workspace'!$J$20:$J$22</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>Click and Collect</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Delivery</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>In Store</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Chart Workspace'!$K$20:$K$22</c:f>
-              <c:numCache>
-                <c:formatCode>"SAR "#,##0</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>12557</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>11838</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>11072</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:firstSliceAng val="0"/>
-        <c:holeSize val="50"/>
-      </c:doughnutChart>
       <c:spPr>
         <a:noFill/>
         <a:ln w="0">
@@ -3004,13 +2379,13 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>160200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>128520</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>32760</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>480960</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>60120</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3018,8 +2393,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="762120"/>
-        <a:ext cx="6119640" cy="2699640"/>
+        <a:off x="0" y="1038240"/>
+        <a:ext cx="6659640" cy="2879640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3031,16 +2406,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>78120</xdr:rowOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>160200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>128520</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>110880</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>405720</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>60120</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3048,8 +2423,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="7562880"/>
-        <a:ext cx="6119640" cy="2699640"/>
+        <a:off x="8045280" y="1038240"/>
+        <a:ext cx="4139640" cy="2879640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3061,16 +2436,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>78120</xdr:rowOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>231840</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>110880</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2589120</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>174600</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3078,8 +2453,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="7260120" y="7562880"/>
-        <a:ext cx="4319640" cy="2699640"/>
+        <a:off x="0" y="9820440"/>
+        <a:ext cx="4139640" cy="2879640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3093,14 +2468,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>78120</xdr:rowOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>26640</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>128520</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>110880</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3129120</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>97200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3108,8 +2483,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="14725800"/>
-        <a:ext cx="6119640" cy="2699640"/>
+        <a:off x="0" y="13077720"/>
+        <a:ext cx="4679640" cy="2699640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3121,16 +2496,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>78120</xdr:rowOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>23040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>128520</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>110880</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>405720</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>93600</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3138,8 +2513,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="20383560"/>
-        <a:ext cx="6119640" cy="2699640"/>
+        <a:off x="8045280" y="13249440"/>
+        <a:ext cx="4139640" cy="2699640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3152,105 +2527,31 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>255960</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>187560</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame>
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Chart 1"/>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="571680"/>
-        <a:ext cx="5759640" cy="3059640"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>255960</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>187560</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame>
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="6" name="Chart 2"/>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="6114960" y="571680"/>
-        <a:ext cx="5759640" cy="3059640"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>290880</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>187560</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame>
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="7" name="Chart 3"/>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="12230280" y="571680"/>
-        <a:ext cx="3959640" cy="3059640"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Lab02Categories" displayName="Lab02Categories" ref="A5:D9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <tableColumns count="4">
+    <tableColumn id="1" name="Category"/>
+    <tableColumn id="2" name="Revenue SAR"/>
+    <tableColumn id="3" name="Orders"/>
+    <tableColumn id="4" name="Average Rating"/>
+  </tableColumns>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Lab02Channels" displayName="Lab02Channels" ref="A5:C8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <tableColumns count="3">
+    <tableColumn id="1" name="Channel"/>
+    <tableColumn id="2" name="Revenue SAR"/>
+    <tableColumn id="3" name="Orders"/>
+  </tableColumns>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChatGPT">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="ChatGPT">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
@@ -3258,46 +2559,46 @@
         <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="0e2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="e8e8e8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="e97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="196b24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="0f9ed5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="a02b93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="4ea72e"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="96607d"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
+        <a:latin typeface="Calibri Light" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Calibri Light" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Calibri Light" pitchFamily="0" charset="1"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
+        <a:ea typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Calibri" pitchFamily="0" charset="1"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -3309,53 +2610,59 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
+                <a:tint val="67000"/>
+                <a:lumMod val="110000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
+                <a:tint val="73000"/>
+                <a:lumMod val="105000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
+                <a:tint val="81000"/>
+                <a:lumMod val="105000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
           <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
+                <a:shade val="78000"/>
+                <a:lumMod val="99000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
           <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
@@ -3374,46 +2681,34 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
+                <a:tint val="93000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
+                <a:tint val="98000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
+                <a:shade val="63000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
           <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
@@ -3425,158 +2720,191 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF17365D"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="13.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="4" style="0" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="B5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="B6" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="4" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="B7" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="4" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+      <c r="B8" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="4" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+      <c r="B9" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="4" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="9" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+    </row>
+    <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
+      <c r="C12" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
+    </row>
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="C13" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="7" t="s">
+    </row>
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="14" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B14" s="4" t="s">
+      <c r="C14" s="15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B15" s="4" t="s">
+      <c r="C15" s="15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="B16" s="4" t="s">
+      <c r="C16" s="15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B17" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>19</v>
+      <c r="C17" s="18" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A11:H11"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C13:C17">
+    <cfRule type="containsText" priority="2" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="Done" dxfId="0">
+      <formula>NOT(ISERROR(SEARCH("Done",C13)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C13:C17" type="list">
+      <formula1>"Not started,In progress,Done"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
@@ -3588,603 +2916,905 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF4472C4"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="13.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
+    <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="B5" s="5" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
+      <c r="C5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="D5" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="7" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="B6" s="19" t="n">
+        <v>6993.6</v>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>120</v>
+      </c>
+      <c r="D6" s="20" t="n">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="B7" s="21" t="n">
+        <v>6567</v>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>120</v>
+      </c>
+      <c r="D7" s="22" t="n">
+        <v>4.09</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="11" t="n">
-        <v>6994</v>
-      </c>
-      <c r="C5" s="12" t="n">
+      <c r="B8" s="21" t="n">
+        <v>11863.8</v>
+      </c>
+      <c r="C8" s="14" t="n">
         <v>120</v>
       </c>
-      <c r="D5" s="13" t="n">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="D8" s="22" t="n">
+        <v>4.19</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="11" t="n">
-        <v>6567</v>
-      </c>
-      <c r="C6" s="12" t="n">
+      <c r="B9" s="23" t="n">
+        <v>10041.7</v>
+      </c>
+      <c r="C9" s="17" t="n">
         <v>120</v>
       </c>
-      <c r="D6" s="13" t="n">
-        <v>4.09</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="11" t="n">
-        <v>11864</v>
-      </c>
-      <c r="C7" s="12" t="n">
-        <v>120</v>
-      </c>
-      <c r="D7" s="13" t="n">
-        <v>4.19</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="11" t="n">
-        <v>10042</v>
-      </c>
-      <c r="C8" s="12" t="n">
-        <v>120</v>
-      </c>
-      <c r="D8" s="13" t="n">
+      <c r="D9" s="24" t="n">
         <v>4.22</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <tableParts>
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF4472C4"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="13.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
+    <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="B5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="10" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="11" t="n">
-        <v>12557</v>
-      </c>
-      <c r="C5" s="12" t="n">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="11" t="n">
-        <v>11838</v>
+      <c r="B6" s="19" t="n">
+        <v>12556.6</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>160</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="11" t="n">
-        <v>11072</v>
-      </c>
-      <c r="C7" s="12" t="n">
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="21" t="n">
+        <v>11837.7</v>
+      </c>
+      <c r="C7" s="15" t="n">
         <v>160</v>
       </c>
     </row>
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="23" t="n">
+        <v>11071.8</v>
+      </c>
+      <c r="C8" s="18" t="n">
+        <v>160</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <tableParts>
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FFE6B800"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L75"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:R72"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="13.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="10"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
+    <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P4" s="25" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="26" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J3" s="2" t="s">
+      <c r="B5" s="26"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
+      <c r="K5" s="26"/>
+      <c r="L5" s="26"/>
+      <c r="M5" s="26"/>
+      <c r="N5" s="26"/>
+      <c r="P5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q5" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="27"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="27"/>
+      <c r="L6" s="27"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27"/>
+      <c r="P6" s="28" t="str">
+        <f aca="false">INDEX('Category Summary'!$A$6:$A$9,MATCH(Q6,'Category Summary'!$B$6:$B$9,0))</f>
+        <v>Snacks</v>
+      </c>
+      <c r="Q6" s="29" t="n">
+        <f aca="false">SMALL('Category Summary'!$B$6:$B$9,1)</f>
+        <v>6567</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="27"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="27"/>
+      <c r="L7" s="27"/>
+      <c r="M7" s="27"/>
+      <c r="N7" s="27"/>
+      <c r="P7" s="28" t="str">
+        <f aca="false">INDEX('Category Summary'!$A$6:$A$9,MATCH(Q7,'Category Summary'!$B$6:$B$9,0))</f>
+        <v>Beverages</v>
+      </c>
+      <c r="Q7" s="29" t="n">
+        <f aca="false">SMALL('Category Summary'!$B$6:$B$9,2)</f>
+        <v>6993.6</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="27"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="27"/>
+      <c r="K8" s="27"/>
+      <c r="L8" s="27"/>
+      <c r="M8" s="27"/>
+      <c r="N8" s="27"/>
+      <c r="P8" s="28" t="str">
+        <f aca="false">INDEX('Category Summary'!$A$6:$A$9,MATCH(Q8,'Category Summary'!$B$6:$B$9,0))</f>
+        <v>Desserts</v>
+      </c>
+      <c r="Q8" s="29" t="n">
+        <f aca="false">SMALL('Category Summary'!$B$6:$B$9,3)</f>
+        <v>10041.7</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="27"/>
+      <c r="K9" s="27"/>
+      <c r="L9" s="27"/>
+      <c r="M9" s="27"/>
+      <c r="N9" s="27"/>
+      <c r="P9" s="28" t="str">
+        <f aca="false">INDEX('Category Summary'!$A$6:$A$9,MATCH(Q9,'Category Summary'!$B$6:$B$9,0))</f>
+        <v>Meals</v>
+      </c>
+      <c r="Q9" s="29" t="n">
+        <f aca="false">SMALL('Category Summary'!$B$6:$B$9,4)</f>
+        <v>11863.8</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="27"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="27"/>
+      <c r="K10" s="27"/>
+      <c r="L10" s="27"/>
+      <c r="M10" s="27"/>
+      <c r="N10" s="27"/>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="27"/>
+      <c r="K11" s="27"/>
+      <c r="L11" s="27"/>
+      <c r="M11" s="27"/>
+      <c r="N11" s="27"/>
+      <c r="P11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q11" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="R11" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="J4" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J5" s="4" t="str">
-        <f aca="false">INDEX('Category Performance'!$A$5:$A$8,MATCH(K5,'Category Performance'!$B$5:$B$8,0))</f>
-        <v>Snacks</v>
-      </c>
-      <c r="K5" s="14" t="n">
-        <f aca="false">SMALL('Category Performance'!$B$5:$B$8,1)</f>
-        <v>6567</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J6" s="4" t="str">
-        <f aca="false">INDEX('Category Performance'!$A$5:$A$8,MATCH(K6,'Category Performance'!$B$5:$B$8,0))</f>
-        <v>Beverages</v>
-      </c>
-      <c r="K6" s="14" t="n">
-        <f aca="false">SMALL('Category Performance'!$B$5:$B$8,2)</f>
-        <v>6994</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J7" s="4" t="str">
-        <f aca="false">INDEX('Category Performance'!$A$5:$A$8,MATCH(K7,'Category Performance'!$B$5:$B$8,0))</f>
-        <v>Desserts</v>
-      </c>
-      <c r="K7" s="14" t="n">
-        <f aca="false">SMALL('Category Performance'!$B$5:$B$8,3)</f>
-        <v>10042</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J8" s="4" t="str">
-        <f aca="false">INDEX('Category Performance'!$A$5:$A$8,MATCH(K8,'Category Performance'!$B$5:$B$8,0))</f>
-        <v>Meals</v>
-      </c>
-      <c r="K8" s="14" t="n">
-        <f aca="false">SMALL('Category Performance'!$B$5:$B$8,4)</f>
-        <v>11864</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J10" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="L10" s="7" t="s">
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="27"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="27"/>
+      <c r="K12" s="27"/>
+      <c r="L12" s="27"/>
+      <c r="M12" s="27"/>
+      <c r="N12" s="27"/>
+      <c r="P12" s="28" t="str">
+        <f aca="false">INDEX('Channel Summary'!$A$6:$A$8,MATCH(Q12,'Channel Summary'!$B$6:$B$8,0))</f>
+        <v>In Store</v>
+      </c>
+      <c r="Q12" s="29" t="n">
+        <f aca="false">SMALL('Channel Summary'!$B$6:$B$8,1)</f>
+        <v>11071.8</v>
+      </c>
+      <c r="R12" s="30" t="n">
+        <f aca="false">Q12/SUM('Channel Summary'!$B$6:$B$8)</f>
+        <v>0.312179799865223</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="27"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="27"/>
+      <c r="K13" s="27"/>
+      <c r="L13" s="27"/>
+      <c r="M13" s="27"/>
+      <c r="N13" s="27"/>
+      <c r="P13" s="28" t="str">
+        <f aca="false">INDEX('Channel Summary'!$A$6:$A$8,MATCH(Q13,'Channel Summary'!$B$6:$B$8,0))</f>
+        <v>Delivery</v>
+      </c>
+      <c r="Q13" s="29" t="n">
+        <f aca="false">SMALL('Channel Summary'!$B$6:$B$8,2)</f>
+        <v>11837.7</v>
+      </c>
+      <c r="R13" s="30" t="n">
+        <f aca="false">Q13/SUM('Channel Summary'!$B$6:$B$8)</f>
+        <v>0.33377506971446</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="27"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="27"/>
+      <c r="K14" s="27"/>
+      <c r="L14" s="27"/>
+      <c r="M14" s="27"/>
+      <c r="N14" s="27"/>
+      <c r="P14" s="28" t="str">
+        <f aca="false">INDEX('Channel Summary'!$A$6:$A$8,MATCH(Q14,'Channel Summary'!$B$6:$B$8,0))</f>
+        <v>Click and Collect</v>
+      </c>
+      <c r="Q14" s="29" t="n">
+        <f aca="false">SMALL('Channel Summary'!$B$6:$B$8,3)</f>
+        <v>12556.6</v>
+      </c>
+      <c r="R14" s="30" t="n">
+        <f aca="false">Q14/SUM('Channel Summary'!$B$6:$B$8)</f>
+        <v>0.354045130420317</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="27"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="27"/>
+      <c r="K15" s="27"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="27"/>
+      <c r="N15" s="27"/>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="27"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="27"/>
+      <c r="K16" s="27"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="27"/>
+      <c r="N16" s="27"/>
+      <c r="P16" s="28" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J11" s="4" t="str">
-        <f aca="false">INDEX('Channel Composition'!$A$5:$A$7,MATCH(K11,'Channel Composition'!$B$5:$B$7,0))</f>
-        <v>In Store</v>
-      </c>
-      <c r="K11" s="14" t="n">
-        <f aca="false">SMALL('Channel Composition'!$B$5:$B$7,1)</f>
-        <v>11072</v>
-      </c>
-      <c r="L11" s="15" t="n">
-        <f aca="false">K11/SUM('Channel Composition'!$B$5:$B$7)</f>
-        <v>0.312177517128598</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J12" s="4" t="str">
-        <f aca="false">INDEX('Channel Composition'!$A$5:$A$7,MATCH(K12,'Channel Composition'!$B$5:$B$7,0))</f>
-        <v>Delivery</v>
-      </c>
-      <c r="K12" s="14" t="n">
-        <f aca="false">SMALL('Channel Composition'!$B$5:$B$7,2)</f>
-        <v>11838</v>
-      </c>
-      <c r="L12" s="15" t="n">
-        <f aca="false">K12/SUM('Channel Composition'!$B$5:$B$7)</f>
-        <v>0.333775058505089</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J13" s="4" t="str">
-        <f aca="false">INDEX('Channel Composition'!$A$5:$A$7,MATCH(K13,'Channel Composition'!$B$5:$B$7,0))</f>
-        <v>Click and Collect</v>
-      </c>
-      <c r="K13" s="14" t="n">
-        <f aca="false">SMALL('Channel Composition'!$B$5:$B$7,3)</f>
-        <v>12557</v>
-      </c>
-      <c r="L13" s="15" t="n">
-        <f aca="false">K13/SUM('Channel Composition'!$B$5:$B$7)</f>
-        <v>0.354047424366312</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J14" s="16" t="s">
+      <c r="Q16" s="29" t="n">
+        <f aca="false">SUM('Channel Summary'!$B$6:$B$8)</f>
+        <v>35466.1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="27"/>
+      <c r="B17" s="27"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="27"/>
+      <c r="J17" s="27"/>
+      <c r="K17" s="27"/>
+      <c r="L17" s="27"/>
+      <c r="M17" s="27"/>
+      <c r="N17" s="27"/>
+      <c r="P17" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="K14" s="17" t="n">
-        <f aca="false">SUM('Channel Composition'!$B$5:$B$7)</f>
-        <v>35467</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J15" s="18" t="s">
+      <c r="Q17" s="29" t="n">
+        <f aca="false">SUM('Category Summary'!$B$6:$B$9)</f>
+        <v>35466.1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="27"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="27"/>
+      <c r="J18" s="27"/>
+      <c r="K18" s="27"/>
+      <c r="L18" s="27"/>
+      <c r="M18" s="27"/>
+      <c r="N18" s="27"/>
+      <c r="P18" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="K15" s="19" t="n">
-        <f aca="false">SUM('Category Performance'!$B$5:$B$8)</f>
-        <v>35467</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J16" s="18" t="s">
+      <c r="Q18" s="28" t="n">
+        <f aca="false">SUM('Channel Summary'!$C$6:$C$8)</f>
+        <v>480</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="27"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="27"/>
+      <c r="K19" s="27"/>
+      <c r="L19" s="27"/>
+      <c r="M19" s="27"/>
+      <c r="N19" s="27"/>
+      <c r="P19" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="K16" s="18" t="n">
-        <f aca="false">SUM('Category Performance'!$C$5:$C$8)</f>
+      <c r="Q19" s="28" t="n">
+        <f aca="false">SUM('Category Summary'!$C$6:$C$9)</f>
         <v>480</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J17" s="18" t="s">
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="27"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="27"/>
+      <c r="J20" s="27"/>
+      <c r="K20" s="27"/>
+      <c r="L20" s="27"/>
+      <c r="M20" s="27"/>
+      <c r="N20" s="27"/>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="K17" s="18" t="n">
-        <f aca="false">SUM('Channel Composition'!$C$5:$C$7)</f>
-        <v>480</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J19" s="7" t="s">
+      <c r="B23" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="K19" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="L19" s="7" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J20" s="4" t="str">
-        <f aca="false">INDEX('Channel Composition'!$A$5:$A$7,MATCH(K20,'Channel Composition'!$B$5:$B$7,0))</f>
-        <v>Click and Collect</v>
-      </c>
-      <c r="K20" s="14" t="n">
-        <f aca="false">LARGE('Channel Composition'!$B$5:$B$7,1)</f>
-        <v>12557</v>
-      </c>
-      <c r="L20" s="15" t="n">
-        <f aca="false">K20/SUM('Channel Composition'!$B$5:$B$7)</f>
-        <v>0.354047424366312</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
+    </row>
+    <row r="24" customFormat="false" ht="139.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B24" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="J21" s="4" t="str">
-        <f aca="false">INDEX('Channel Composition'!$A$5:$A$7,MATCH(K21,'Channel Composition'!$B$5:$B$7,0))</f>
-        <v>Delivery</v>
-      </c>
-      <c r="K21" s="14" t="n">
-        <f aca="false">LARGE('Channel Composition'!$B$5:$B$7,2)</f>
-        <v>11838</v>
-      </c>
-      <c r="L21" s="15" t="n">
-        <f aca="false">K21/SUM('Channel Composition'!$B$5:$B$7)</f>
-        <v>0.333775058505089</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="20" t="s">
+    </row>
+    <row r="25" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="B25" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="J22" s="4" t="str">
-        <f aca="false">INDEX('Channel Composition'!$A$5:$A$7,MATCH(K22,'Channel Composition'!$B$5:$B$7,0))</f>
-        <v>In Store</v>
-      </c>
-      <c r="K22" s="14" t="n">
-        <f aca="false">LARGE('Channel Composition'!$B$5:$B$7,3)</f>
-        <v>11072</v>
-      </c>
-      <c r="L22" s="15" t="n">
-        <f aca="false">K22/SUM('Channel Composition'!$B$5:$B$7)</f>
-        <v>0.312177517128598</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="20" t="s">
+    </row>
+    <row r="26" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="B23" s="21" t="s">
+      <c r="B26" s="34" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="20" t="s">
+    <row r="27" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="B24" s="21" t="s">
+      <c r="B27" s="36" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="20" t="s">
+    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="B25" s="21" t="s">
+    </row>
+    <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H31" s="38" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="s">
+      <c r="I31" s="38"/>
+      <c r="J31" s="38"/>
+      <c r="K31" s="38"/>
+      <c r="L31" s="38"/>
+      <c r="M31" s="38"/>
+      <c r="N31" s="38"/>
+    </row>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H32" s="38"/>
+      <c r="I32" s="38"/>
+      <c r="J32" s="38"/>
+      <c r="K32" s="38"/>
+      <c r="L32" s="38"/>
+      <c r="M32" s="38"/>
+      <c r="N32" s="38"/>
+    </row>
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H33" s="38"/>
+      <c r="I33" s="38"/>
+      <c r="J33" s="38"/>
+      <c r="K33" s="38"/>
+      <c r="L33" s="38"/>
+      <c r="M33" s="38"/>
+      <c r="N33" s="38"/>
+    </row>
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H34" s="38"/>
+      <c r="I34" s="38"/>
+      <c r="J34" s="38"/>
+      <c r="K34" s="38"/>
+      <c r="L34" s="38"/>
+      <c r="M34" s="38"/>
+      <c r="N34" s="38"/>
+    </row>
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H35" s="38"/>
+      <c r="I35" s="38"/>
+      <c r="J35" s="38"/>
+      <c r="K35" s="38"/>
+      <c r="L35" s="38"/>
+      <c r="M35" s="38"/>
+      <c r="N35" s="38"/>
+    </row>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H36" s="38"/>
+      <c r="I36" s="38"/>
+      <c r="J36" s="38"/>
+      <c r="K36" s="38"/>
+      <c r="L36" s="38"/>
+      <c r="M36" s="38"/>
+      <c r="N36" s="38"/>
+    </row>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H37" s="38"/>
+      <c r="I37" s="38"/>
+      <c r="J37" s="38"/>
+      <c r="K37" s="38"/>
+      <c r="L37" s="38"/>
+      <c r="M37" s="38"/>
+      <c r="N37" s="38"/>
+    </row>
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H38" s="38"/>
+      <c r="I38" s="38"/>
+      <c r="J38" s="38"/>
+      <c r="K38" s="38"/>
+      <c r="L38" s="38"/>
+      <c r="M38" s="38"/>
+      <c r="N38" s="38"/>
+    </row>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="J27" s="10" t="s">
+    </row>
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="39" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="J44" s="22" t="s">
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H50" s="40" t="s">
         <v>63</v>
       </c>
-      <c r="K44" s="22"/>
-      <c r="L44" s="22"/>
-    </row>
-    <row r="45" customFormat="false" ht="97.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="B45" s="21" t="s">
+    </row>
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="41" t="s">
         <v>64</v>
       </c>
-      <c r="J45" s="22"/>
-      <c r="K45" s="22"/>
-      <c r="L45" s="22"/>
-    </row>
-    <row r="46" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="B46" s="21" t="s">
+    </row>
+    <row r="68" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="38" t="s">
         <v>65</v>
       </c>
-      <c r="J46" s="22"/>
-      <c r="K46" s="22"/>
-      <c r="L46" s="22"/>
-    </row>
-    <row r="47" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="B47" s="21" t="s">
+      <c r="B68" s="38"/>
+      <c r="C68" s="38"/>
+      <c r="D68" s="38"/>
+      <c r="E68" s="38"/>
+      <c r="F68" s="38"/>
+      <c r="G68" s="38"/>
+      <c r="H68" s="38"/>
+      <c r="I68" s="38"/>
+      <c r="J68" s="38"/>
+      <c r="K68" s="38"/>
+      <c r="L68" s="38"/>
+      <c r="M68" s="38"/>
+      <c r="N68" s="38"/>
+    </row>
+    <row r="69" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="38" t="s">
         <v>66</v>
       </c>
-      <c r="J47" s="22"/>
-      <c r="K47" s="22"/>
-      <c r="L47" s="22"/>
-    </row>
-    <row r="48" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="B48" s="21" t="s">
+      <c r="B69" s="38"/>
+      <c r="C69" s="38"/>
+      <c r="D69" s="38"/>
+      <c r="E69" s="38"/>
+      <c r="F69" s="38"/>
+      <c r="G69" s="38"/>
+      <c r="H69" s="38"/>
+      <c r="I69" s="38"/>
+      <c r="J69" s="38"/>
+      <c r="K69" s="38"/>
+      <c r="L69" s="38"/>
+      <c r="M69" s="38"/>
+      <c r="N69" s="38"/>
+    </row>
+    <row r="71" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="41" t="s">
         <v>67</v>
       </c>
-      <c r="J48" s="22"/>
-      <c r="K48" s="22"/>
-      <c r="L48" s="22"/>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="5" t="s">
+    </row>
+    <row r="72" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="B50" s="6"/>
-      <c r="C50" s="6"/>
-      <c r="D50" s="6"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="6"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="23" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="10" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="B69" s="22"/>
-      <c r="C69" s="22"/>
-      <c r="D69" s="22"/>
-      <c r="E69" s="22"/>
-      <c r="F69" s="22"/>
-      <c r="G69" s="22"/>
-      <c r="H69" s="22"/>
-    </row>
-    <row r="70" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="B70" s="22"/>
-      <c r="C70" s="22"/>
-      <c r="D70" s="22"/>
-      <c r="E70" s="22"/>
-      <c r="F70" s="22"/>
-      <c r="G70" s="22"/>
-      <c r="H70" s="22"/>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="10" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="B73" s="22"/>
-      <c r="C73" s="22"/>
-      <c r="D73" s="22"/>
-      <c r="E73" s="22"/>
-      <c r="F73" s="22"/>
-      <c r="G73" s="22"/>
-      <c r="H73" s="22"/>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="24" t="s">
-        <v>75</v>
-      </c>
+      <c r="B72" s="38"/>
+      <c r="C72" s="38"/>
+      <c r="D72" s="38"/>
+      <c r="E72" s="38"/>
+      <c r="F72" s="38"/>
+      <c r="G72" s="38"/>
+      <c r="H72" s="38"/>
+      <c r="I72" s="38"/>
+      <c r="J72" s="38"/>
+      <c r="K72" s="38"/>
+      <c r="L72" s="38"/>
+      <c r="M72" s="38"/>
+      <c r="N72" s="38"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="J44:L48"/>
-    <mergeCell ref="A69:H69"/>
-    <mergeCell ref="A70:H70"/>
-    <mergeCell ref="A73:H73"/>
+  <mergeCells count="8">
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="H5:N5"/>
+    <mergeCell ref="H31:N38"/>
+    <mergeCell ref="A68:N68"/>
+    <mergeCell ref="A69:N69"/>
+    <mergeCell ref="A72:N72"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
@@ -4192,34 +3822,4 @@
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="true"/>
-  </sheetPr>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="25" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
-</worksheet>
 </file>
--- a/lab02/APIO114_Lab02_2713963.xlsx
+++ b/lab02/APIO114_Lab02_2713963.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="72">
   <si>
     <t xml:space="preserve">Lab 2 Chart Choice and Visual Design</t>
   </si>
@@ -31,7 +31,16 @@
     <t xml:space="preserve">APIO 114 Data Visualization | Semester 2027-01</t>
   </si>
   <si>
-    <t xml:space="preserve">Student: اروى حمدان الحربي  |  ID: 2713963</t>
+    <t xml:space="preserve">Student name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اروى حمدان الحربي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2713963</t>
   </si>
   <si>
     <t xml:space="preserve">Duration</t>
@@ -283,21 +292,14 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF222222"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -342,6 +344,13 @@
       <b val="true"/>
       <sz val="10"/>
       <color rgb="FF008000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -402,15 +411,6 @@
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF17365D"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
         <color rgb="FFFFFFFF"/>
       </left>
@@ -428,7 +428,9 @@
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
       </bottom>
@@ -437,9 +439,16 @@
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
-      <top style="thin">
-        <color rgb="FFD9D9D9"/>
-      </top>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF17365D"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
       </bottom>
@@ -604,31 +613,31 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -692,11 +701,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -704,59 +713,59 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1062,11 +1071,11 @@
         </c:ser>
         <c:gapWidth val="55"/>
         <c:overlap val="0"/>
-        <c:axId val="40541759"/>
-        <c:axId val="46134616"/>
+        <c:axId val="56352799"/>
+        <c:axId val="89909192"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="40541759"/>
+        <c:axId val="56352799"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1099,7 +1108,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="46134616"/>
+        <c:crossAx val="89909192"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1107,7 +1116,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="46134616"/>
+        <c:axId val="89909192"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -1177,7 +1186,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40541759"/>
+        <c:crossAx val="56352799"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1385,11 +1394,11 @@
         </c:ser>
         <c:gapWidth val="55"/>
         <c:overlap val="0"/>
-        <c:axId val="19682116"/>
-        <c:axId val="80492597"/>
+        <c:axId val="18387022"/>
+        <c:axId val="12097278"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="19682116"/>
+        <c:axId val="18387022"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1422,7 +1431,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80492597"/>
+        <c:crossAx val="12097278"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1430,7 +1439,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="80492597"/>
+        <c:axId val="12097278"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -1500,7 +1509,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="19682116"/>
+        <c:crossAx val="18387022"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1931,11 +1940,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="50166213"/>
-        <c:axId val="70985252"/>
+        <c:axId val="67265759"/>
+        <c:axId val="60751017"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="50166213"/>
+        <c:axId val="67265759"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1968,7 +1977,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70985252"/>
+        <c:crossAx val="60751017"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1976,7 +1985,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="70985252"/>
+        <c:axId val="60751017"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="13000"/>
@@ -2021,7 +2030,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="50166213"/>
+        <c:crossAx val="67265759"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2229,11 +2238,11 @@
         </c:ser>
         <c:gapWidth val="55"/>
         <c:overlap val="0"/>
-        <c:axId val="29310303"/>
-        <c:axId val="64952816"/>
+        <c:axId val="73928420"/>
+        <c:axId val="9868512"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="29310303"/>
+        <c:axId val="73928420"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2266,7 +2275,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="64952816"/>
+        <c:crossAx val="9868512"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2274,7 +2283,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="64952816"/>
+        <c:axId val="9868512"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2344,7 +2353,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29310303"/>
+        <c:crossAx val="73928420"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2756,61 +2765,71 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
+      <c r="B3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+    </row>
+    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
-        <v>3</v>
+      <c r="A5" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
-        <v>5</v>
+      <c r="A6" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
-        <v>7</v>
+      <c r="A7" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
-        <v>9</v>
+      <c r="A8" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
-        <v>11</v>
+      <c r="A9" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -2821,14 +2840,14 @@
       <c r="H11" s="9"/>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>16</v>
+      <c r="A12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2836,10 +2855,10 @@
         <v>1</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2847,10 +2866,10 @@
         <v>2</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2858,10 +2877,10 @@
         <v>3</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2869,10 +2888,10 @@
         <v>4</v>
       </c>
       <c r="B16" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="15" t="s">
         <v>21</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2880,10 +2899,10 @@
         <v>5</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -2930,7 +2949,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2938,35 +2957,35 @@
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="A5" s="3" t="s">
         <v>28</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B6" s="19" t="n">
         <v>6993.6</v>
@@ -2980,7 +2999,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B7" s="21" t="n">
         <v>6567</v>
@@ -2994,7 +3013,7 @@
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B8" s="21" t="n">
         <v>11863.8</v>
@@ -3008,7 +3027,7 @@
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B9" s="23" t="n">
         <v>10041.7</v>
@@ -3054,37 +3073,37 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>27</v>
+      <c r="A5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B6" s="19" t="n">
         <v>12556.6</v>
@@ -3095,7 +3114,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B7" s="21" t="n">
         <v>11837.7</v>
@@ -3106,7 +3125,7 @@
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B8" s="23" t="n">
         <v>11071.8</v>
@@ -3151,7 +3170,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3169,7 +3188,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3186,29 +3205,29 @@
       <c r="N2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="P4" s="25" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="26" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B5" s="26"/>
       <c r="C5" s="26"/>
@@ -3217,7 +3236,7 @@
       <c r="F5" s="26"/>
       <c r="G5" s="26"/>
       <c r="H5" s="26" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="I5" s="26"/>
       <c r="J5" s="26"/>
@@ -3225,11 +3244,11 @@
       <c r="L5" s="26"/>
       <c r="M5" s="26"/>
       <c r="N5" s="26"/>
-      <c r="P5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q5" s="5" t="s">
-        <v>26</v>
+      <c r="P5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3359,14 +3378,14 @@
       <c r="L11" s="27"/>
       <c r="M11" s="27"/>
       <c r="N11" s="27"/>
-      <c r="P11" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q11" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="R11" s="5" t="s">
-        <v>44</v>
+      <c r="P11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="R11" s="3" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3485,7 +3504,7 @@
       <c r="M16" s="27"/>
       <c r="N16" s="27"/>
       <c r="P16" s="28" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q16" s="29" t="n">
         <f aca="false">SUM('Channel Summary'!$B$6:$B$8)</f>
@@ -3508,7 +3527,7 @@
       <c r="M17" s="27"/>
       <c r="N17" s="27"/>
       <c r="P17" s="28" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="Q17" s="29" t="n">
         <f aca="false">SUM('Category Summary'!$B$6:$B$9)</f>
@@ -3531,7 +3550,7 @@
       <c r="M18" s="27"/>
       <c r="N18" s="27"/>
       <c r="P18" s="28" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="Q18" s="28" t="n">
         <f aca="false">SUM('Channel Summary'!$C$6:$C$8)</f>
@@ -3554,7 +3573,7 @@
       <c r="M19" s="27"/>
       <c r="N19" s="27"/>
       <c r="P19" s="28" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="Q19" s="28" t="n">
         <f aca="false">SUM('Category Summary'!$C$6:$C$9)</f>
@@ -3580,53 +3599,53 @@
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>50</v>
+      <c r="A23" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="139.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="31" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B24" s="32" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="33" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B25" s="34" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="33" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B26" s="34" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="35" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="37" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H31" s="38" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I31" s="38"/>
       <c r="J31" s="38"/>
@@ -3709,17 +3728,17 @@
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="37" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="39" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H50" s="40" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -3740,12 +3759,12 @@
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="41" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="38" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B68" s="38"/>
       <c r="C68" s="38"/>
@@ -3763,7 +3782,7 @@
     </row>
     <row r="69" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="38" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B69" s="38"/>
       <c r="C69" s="38"/>
@@ -3781,12 +3800,12 @@
     </row>
     <row r="71" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="41" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="38" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B72" s="38"/>
       <c r="C72" s="38"/>
